--- a/프로젝트_신용등급분류/데이터 컬럼 설명.xlsx
+++ b/프로젝트_신용등급분류/데이터 컬럼 설명.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\workspace\intensive2504\프로젝트_신용등급분류\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2252201E-413E-42E9-B8D7-FCC16CBA51AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0D1F6E-8076-484A-820E-10F7E8719C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{18B70014-FB54-4024-A698-DEB134D08611}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{18B70014-FB54-4024-A698-DEB134D08611}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>변수명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,6 +161,35 @@
   <si>
     <t>1: 기본값, 대출금 체납한 경우
 0: 기본값아님, 채무 불이행 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loan_percent_income</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대출 금액이 차지하는 소득의 비율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_person_default_on_file</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신용 조사 기관 기록에 따른 개인의 과거 채무 불이행 현황</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y: 해당 개인은 신용 기록에 채무 불이행 기록이 있음
+N: 해당 개인은 채무 불이행 이력이 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cb_person_cred_hist_length</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개인의 신용 이력 기간</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -202,7 +231,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +241,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -230,7 +271,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -241,6 +282,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -557,11 +604,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89F95E4-5613-41B2-9F8B-C6B4307FE5D9}">
-  <dimension ref="C5:G14"/>
+  <dimension ref="C5:G17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="23.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="73" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="71.25" customWidth="1"/>
   </cols>
@@ -645,7 +692,7 @@
       </c>
     </row>
     <row r="11" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D11" t="s">
@@ -670,7 +717,7 @@
       </c>
     </row>
     <row r="13" spans="3:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D13" t="s">
@@ -697,8 +744,45 @@
         <v>29</v>
       </c>
     </row>
+    <row r="15" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>